--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eis2win-my.sharepoint.com/personal/caroline_adams_uksportsinstitute_co_uk/Documents/Documents/16_Msc_Biomech/Professional Practice/Assessment 2/Repo_Biomech_dashboard/Prof_Practice_Report/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{982CBBF7-6A9D-48B0-AF85-454491A8D7F1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="46">
   <si>
     <t>Cycle</t>
   </si>
@@ -145,6 +146,39 @@
   <si>
     <t>35-45</t>
   </si>
+  <si>
+    <t>60m_3</t>
+  </si>
+  <si>
+    <t>Rep3</t>
+  </si>
+  <si>
+    <t>Cycle Length (m)</t>
+  </si>
+  <si>
+    <t>Push Dist (m)</t>
+  </si>
+  <si>
+    <t>Recovery Dist (m)</t>
+  </si>
+  <si>
+    <t>Push Angle (deg)</t>
+  </si>
+  <si>
+    <t>Cycle Freq (Hz)</t>
+  </si>
+  <si>
+    <t>Push time (secs)</t>
+  </si>
+  <si>
+    <t>Recovery time (secs)</t>
+  </si>
+  <si>
+    <t>Avg Cycle Speed (m/s)</t>
+  </si>
+  <si>
+    <t>third</t>
+  </si>
 </sst>
 </file>
 
@@ -165,12 +199,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -185,12 +225,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9ED8C8E-FDDF-49A2-ABF2-02E1268CE5AD}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2876,6 +2920,5106 @@
         <v>33</v>
       </c>
     </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2">
+        <f>R78</f>
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" t="s">
+        <v>45</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2">
+        <f>S78</f>
+        <v>0</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" s="2">
+        <f>V78</f>
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" s="2">
+        <f>W78</f>
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="2">
+        <f>T78</f>
+        <v>0</v>
+      </c>
+      <c r="I78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1</v>
+      </c>
+      <c r="B79" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2">
+        <f>Q78</f>
+        <v>0</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="2">
+        <f>U78</f>
+        <v>0</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" s="2">
+        <f>X78</f>
+        <v>0</v>
+      </c>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2">
+        <f>R79</f>
+        <v>0</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" t="s">
+        <v>45</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2">
+        <f>S79</f>
+        <v>0</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84" s="2">
+        <f>V79</f>
+        <v>0</v>
+      </c>
+      <c r="I84" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>31</v>
+      </c>
+      <c r="H85" s="2">
+        <f>W79</f>
+        <v>0</v>
+      </c>
+      <c r="I85" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2">
+        <f>T79</f>
+        <v>0</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>30</v>
+      </c>
+      <c r="H87" s="2">
+        <f>Q79</f>
+        <v>0</v>
+      </c>
+      <c r="I87" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88" t="s">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="2">
+        <f>U79</f>
+        <v>0</v>
+      </c>
+      <c r="I88" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="2">
+        <f>X79</f>
+        <v>0</v>
+      </c>
+      <c r="I89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>35</v>
+      </c>
+      <c r="C90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s">
+        <v>30</v>
+      </c>
+      <c r="H90" s="2">
+        <f>R80</f>
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" t="s">
+        <v>30</v>
+      </c>
+      <c r="H91" s="2">
+        <f>S80</f>
+        <v>0</v>
+      </c>
+      <c r="I91" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" t="s">
+        <v>31</v>
+      </c>
+      <c r="H92" s="2">
+        <f>V80</f>
+        <v>0</v>
+      </c>
+      <c r="I92" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>31</v>
+      </c>
+      <c r="H93" s="2">
+        <f>W80</f>
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1</v>
+      </c>
+      <c r="B94" t="s">
+        <v>35</v>
+      </c>
+      <c r="C94" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="2">
+        <f>T80</f>
+        <v>0</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>35</v>
+      </c>
+      <c r="C95" t="s">
+        <v>45</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95">
+        <v>3</v>
+      </c>
+      <c r="F95" t="s">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2">
+        <f>Q80</f>
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>1</v>
+      </c>
+      <c r="B96" t="s">
+        <v>35</v>
+      </c>
+      <c r="C96" t="s">
+        <v>45</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96" t="s">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="2">
+        <f>U80</f>
+        <v>0</v>
+      </c>
+      <c r="I96" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>1</v>
+      </c>
+      <c r="B97" t="s">
+        <v>35</v>
+      </c>
+      <c r="C97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97" t="s">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" s="2">
+        <f>X80</f>
+        <v>0</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>1</v>
+      </c>
+      <c r="B98" t="s">
+        <v>35</v>
+      </c>
+      <c r="C98" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98">
+        <v>4</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" t="s">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2">
+        <f>R81</f>
+        <v>0</v>
+      </c>
+      <c r="I98" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2">
+        <f>S81</f>
+        <v>0</v>
+      </c>
+      <c r="I99" t="s">
+        <v>15</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>1</v>
+      </c>
+      <c r="B100" t="s">
+        <v>35</v>
+      </c>
+      <c r="C100" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+      <c r="F100" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>31</v>
+      </c>
+      <c r="H100" s="2">
+        <f>V81</f>
+        <v>0</v>
+      </c>
+      <c r="I100" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" t="s">
+        <v>45</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" t="s">
+        <v>31</v>
+      </c>
+      <c r="H101" s="2">
+        <f>W81</f>
+        <v>0</v>
+      </c>
+      <c r="I101" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102">
+        <v>4</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="2">
+        <f>T81</f>
+        <v>0</v>
+      </c>
+      <c r="I102" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>1</v>
+      </c>
+      <c r="B103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" t="s">
+        <v>45</v>
+      </c>
+      <c r="D103" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103">
+        <v>4</v>
+      </c>
+      <c r="F103" t="s">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2">
+        <f>Q81</f>
+        <v>0</v>
+      </c>
+      <c r="I103" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>35</v>
+      </c>
+      <c r="C104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+      <c r="F104" t="s">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="2">
+        <f>U81</f>
+        <v>0</v>
+      </c>
+      <c r="I104" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" t="s">
+        <v>45</v>
+      </c>
+      <c r="D105" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105">
+        <v>4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>21</v>
+      </c>
+      <c r="H105" s="2">
+        <f>X81</f>
+        <v>0</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>35</v>
+      </c>
+      <c r="C106" t="s">
+        <v>45</v>
+      </c>
+      <c r="D106" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106">
+        <v>5</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>30</v>
+      </c>
+      <c r="H106" s="2">
+        <f>R82</f>
+        <v>0</v>
+      </c>
+      <c r="I106" t="s">
+        <v>15</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>1</v>
+      </c>
+      <c r="B107" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107">
+        <v>5</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>30</v>
+      </c>
+      <c r="H107" s="2">
+        <f>S82</f>
+        <v>0</v>
+      </c>
+      <c r="I107" t="s">
+        <v>15</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>35</v>
+      </c>
+      <c r="C108" t="s">
+        <v>45</v>
+      </c>
+      <c r="D108" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108">
+        <v>5</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>31</v>
+      </c>
+      <c r="H108" s="2">
+        <f>V82</f>
+        <v>0</v>
+      </c>
+      <c r="I108" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>1</v>
+      </c>
+      <c r="B109" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>31</v>
+      </c>
+      <c r="H109" s="2">
+        <f>W82</f>
+        <v>0</v>
+      </c>
+      <c r="I109" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>35</v>
+      </c>
+      <c r="C110" t="s">
+        <v>45</v>
+      </c>
+      <c r="D110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110">
+        <v>5</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="2">
+        <f>T82</f>
+        <v>0</v>
+      </c>
+      <c r="I110" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>35</v>
+      </c>
+      <c r="C111" t="s">
+        <v>45</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
+        <v>30</v>
+      </c>
+      <c r="H111" s="2">
+        <f>Q82</f>
+        <v>0</v>
+      </c>
+      <c r="I111" t="s">
+        <v>15</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>45</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112" t="s">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>22</v>
+      </c>
+      <c r="H112" s="2">
+        <f>U82</f>
+        <v>0</v>
+      </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>35</v>
+      </c>
+      <c r="C113" t="s">
+        <v>45</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113">
+        <v>5</v>
+      </c>
+      <c r="F113" t="s">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>21</v>
+      </c>
+      <c r="H113" s="2">
+        <f>X82</f>
+        <v>0</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>35</v>
+      </c>
+      <c r="C114" t="s">
+        <v>45</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>30</v>
+      </c>
+      <c r="H114" s="2">
+        <f>R83</f>
+        <v>0</v>
+      </c>
+      <c r="I114" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115" t="s">
+        <v>45</v>
+      </c>
+      <c r="D115" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115">
+        <v>6</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>30</v>
+      </c>
+      <c r="H115" s="2">
+        <f>S83</f>
+        <v>0</v>
+      </c>
+      <c r="I115" t="s">
+        <v>15</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>35</v>
+      </c>
+      <c r="C116" t="s">
+        <v>45</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116">
+        <v>6</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>31</v>
+      </c>
+      <c r="H116" s="2">
+        <f>V83</f>
+        <v>0</v>
+      </c>
+      <c r="I116" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117" t="s">
+        <v>45</v>
+      </c>
+      <c r="D117" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117">
+        <v>6</v>
+      </c>
+      <c r="F117" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117" t="s">
+        <v>31</v>
+      </c>
+      <c r="H117" s="2">
+        <f>W83</f>
+        <v>0</v>
+      </c>
+      <c r="I117" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>35</v>
+      </c>
+      <c r="C118" t="s">
+        <v>45</v>
+      </c>
+      <c r="D118" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118">
+        <v>6</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="2">
+        <f>T83</f>
+        <v>0</v>
+      </c>
+      <c r="I118" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>35</v>
+      </c>
+      <c r="C119" t="s">
+        <v>45</v>
+      </c>
+      <c r="D119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119">
+        <v>6</v>
+      </c>
+      <c r="F119" t="s">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
+        <v>30</v>
+      </c>
+      <c r="H119" s="2">
+        <f>Q83</f>
+        <v>0</v>
+      </c>
+      <c r="I119" t="s">
+        <v>15</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>35</v>
+      </c>
+      <c r="C120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120">
+        <v>6</v>
+      </c>
+      <c r="F120" t="s">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>22</v>
+      </c>
+      <c r="H120" s="2">
+        <f>U83</f>
+        <v>0</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>35</v>
+      </c>
+      <c r="C121" t="s">
+        <v>45</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121">
+        <v>6</v>
+      </c>
+      <c r="F121" t="s">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>21</v>
+      </c>
+      <c r="H121" s="2">
+        <f>X83</f>
+        <v>0</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>35</v>
+      </c>
+      <c r="C122" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" t="s">
+        <v>34</v>
+      </c>
+      <c r="E122">
+        <v>17</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>30</v>
+      </c>
+      <c r="H122" s="2">
+        <f>R84</f>
+        <v>0</v>
+      </c>
+      <c r="I122" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>35</v>
+      </c>
+      <c r="C123" t="s">
+        <v>45</v>
+      </c>
+      <c r="D123" t="s">
+        <v>34</v>
+      </c>
+      <c r="E123">
+        <v>17</v>
+      </c>
+      <c r="F123" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>30</v>
+      </c>
+      <c r="H123" s="2">
+        <f>S84</f>
+        <v>0</v>
+      </c>
+      <c r="I123" t="s">
+        <v>15</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>35</v>
+      </c>
+      <c r="C124" t="s">
+        <v>45</v>
+      </c>
+      <c r="D124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E124">
+        <v>17</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" t="s">
+        <v>31</v>
+      </c>
+      <c r="H124" s="2">
+        <f>V84</f>
+        <v>0</v>
+      </c>
+      <c r="I124" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" t="s">
+        <v>34</v>
+      </c>
+      <c r="E125">
+        <v>17</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>31</v>
+      </c>
+      <c r="H125" s="2">
+        <f>W84</f>
+        <v>0</v>
+      </c>
+      <c r="I125" t="s">
+        <v>16</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>35</v>
+      </c>
+      <c r="C126" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" t="s">
+        <v>34</v>
+      </c>
+      <c r="E126">
+        <v>17</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="2">
+        <f>T84</f>
+        <v>0</v>
+      </c>
+      <c r="I126" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>35</v>
+      </c>
+      <c r="C127" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" t="s">
+        <v>34</v>
+      </c>
+      <c r="E127">
+        <v>17</v>
+      </c>
+      <c r="F127" t="s">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2">
+        <f>Q84</f>
+        <v>0</v>
+      </c>
+      <c r="I127" t="s">
+        <v>15</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>35</v>
+      </c>
+      <c r="C128" t="s">
+        <v>45</v>
+      </c>
+      <c r="D128" t="s">
+        <v>34</v>
+      </c>
+      <c r="E128">
+        <v>17</v>
+      </c>
+      <c r="F128" t="s">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
+        <v>22</v>
+      </c>
+      <c r="H128" s="2">
+        <f>U84</f>
+        <v>0</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129" t="s">
+        <v>45</v>
+      </c>
+      <c r="D129" t="s">
+        <v>34</v>
+      </c>
+      <c r="E129">
+        <v>17</v>
+      </c>
+      <c r="F129" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>21</v>
+      </c>
+      <c r="H129" s="2">
+        <f>X84</f>
+        <v>0</v>
+      </c>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130" t="s">
+        <v>45</v>
+      </c>
+      <c r="D130" t="s">
+        <v>34</v>
+      </c>
+      <c r="E130">
+        <v>18</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130" s="2">
+        <f>R85</f>
+        <v>0</v>
+      </c>
+      <c r="I130" t="s">
+        <v>15</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>1</v>
+      </c>
+      <c r="B131" t="s">
+        <v>35</v>
+      </c>
+      <c r="C131" t="s">
+        <v>45</v>
+      </c>
+      <c r="D131" t="s">
+        <v>34</v>
+      </c>
+      <c r="E131">
+        <v>18</v>
+      </c>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" t="s">
+        <v>30</v>
+      </c>
+      <c r="H131" s="2">
+        <f>S85</f>
+        <v>0</v>
+      </c>
+      <c r="I131" t="s">
+        <v>15</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>1</v>
+      </c>
+      <c r="B132" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" t="s">
+        <v>45</v>
+      </c>
+      <c r="D132" t="s">
+        <v>34</v>
+      </c>
+      <c r="E132">
+        <v>18</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" t="s">
+        <v>31</v>
+      </c>
+      <c r="H132" s="2">
+        <f>V85</f>
+        <v>0</v>
+      </c>
+      <c r="I132" t="s">
+        <v>16</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>35</v>
+      </c>
+      <c r="C133" t="s">
+        <v>45</v>
+      </c>
+      <c r="D133" t="s">
+        <v>34</v>
+      </c>
+      <c r="E133">
+        <v>18</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>31</v>
+      </c>
+      <c r="H133" s="2">
+        <f>W85</f>
+        <v>0</v>
+      </c>
+      <c r="I133" t="s">
+        <v>16</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>35</v>
+      </c>
+      <c r="C134" t="s">
+        <v>45</v>
+      </c>
+      <c r="D134" t="s">
+        <v>34</v>
+      </c>
+      <c r="E134">
+        <v>18</v>
+      </c>
+      <c r="F134" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" t="s">
+        <v>20</v>
+      </c>
+      <c r="H134" s="2">
+        <f>T85</f>
+        <v>0</v>
+      </c>
+      <c r="I134" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>35</v>
+      </c>
+      <c r="C135" t="s">
+        <v>45</v>
+      </c>
+      <c r="D135" t="s">
+        <v>34</v>
+      </c>
+      <c r="E135">
+        <v>18</v>
+      </c>
+      <c r="F135" t="s">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>30</v>
+      </c>
+      <c r="H135" s="2">
+        <f>Q85</f>
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>15</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>35</v>
+      </c>
+      <c r="C136" t="s">
+        <v>45</v>
+      </c>
+      <c r="D136" t="s">
+        <v>34</v>
+      </c>
+      <c r="E136">
+        <v>18</v>
+      </c>
+      <c r="F136" t="s">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>22</v>
+      </c>
+      <c r="H136" s="2">
+        <f>U85</f>
+        <v>0</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137" t="s">
+        <v>45</v>
+      </c>
+      <c r="D137" t="s">
+        <v>34</v>
+      </c>
+      <c r="E137">
+        <v>18</v>
+      </c>
+      <c r="F137" t="s">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>21</v>
+      </c>
+      <c r="H137" s="2">
+        <f>X85</f>
+        <v>0</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>35</v>
+      </c>
+      <c r="C138" t="s">
+        <v>45</v>
+      </c>
+      <c r="D138" t="s">
+        <v>34</v>
+      </c>
+      <c r="E138">
+        <v>19</v>
+      </c>
+      <c r="F138" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" t="s">
+        <v>30</v>
+      </c>
+      <c r="H138" s="2">
+        <f>Q86</f>
+        <v>0</v>
+      </c>
+      <c r="I138" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>1</v>
+      </c>
+      <c r="B139" t="s">
+        <v>35</v>
+      </c>
+      <c r="C139" t="s">
+        <v>45</v>
+      </c>
+      <c r="D139" t="s">
+        <v>34</v>
+      </c>
+      <c r="E139">
+        <v>19</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
+        <v>30</v>
+      </c>
+      <c r="H139" s="2">
+        <f>R86</f>
+        <v>0</v>
+      </c>
+      <c r="I139" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140" t="s">
+        <v>45</v>
+      </c>
+      <c r="D140" t="s">
+        <v>34</v>
+      </c>
+      <c r="E140">
+        <v>19</v>
+      </c>
+      <c r="F140" t="s">
+        <v>13</v>
+      </c>
+      <c r="G140" t="s">
+        <v>31</v>
+      </c>
+      <c r="H140" s="2">
+        <f>V86</f>
+        <v>0</v>
+      </c>
+      <c r="I140" t="s">
+        <v>16</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>35</v>
+      </c>
+      <c r="C141" t="s">
+        <v>45</v>
+      </c>
+      <c r="D141" t="s">
+        <v>34</v>
+      </c>
+      <c r="E141">
+        <v>19</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>31</v>
+      </c>
+      <c r="H141" s="2">
+        <f>W86</f>
+        <v>0</v>
+      </c>
+      <c r="I141" t="s">
+        <v>16</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>35</v>
+      </c>
+      <c r="C142" t="s">
+        <v>45</v>
+      </c>
+      <c r="D142" t="s">
+        <v>34</v>
+      </c>
+      <c r="E142">
+        <v>19</v>
+      </c>
+      <c r="F142" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" t="s">
+        <v>20</v>
+      </c>
+      <c r="H142" s="2">
+        <f>T86</f>
+        <v>0</v>
+      </c>
+      <c r="I142" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>35</v>
+      </c>
+      <c r="C143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D143" t="s">
+        <v>34</v>
+      </c>
+      <c r="E143">
+        <v>19</v>
+      </c>
+      <c r="F143" t="s">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>30</v>
+      </c>
+      <c r="H143" s="2">
+        <f>P86</f>
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
+        <v>15</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>35</v>
+      </c>
+      <c r="C144" t="s">
+        <v>45</v>
+      </c>
+      <c r="D144" t="s">
+        <v>34</v>
+      </c>
+      <c r="E144">
+        <v>19</v>
+      </c>
+      <c r="F144" t="s">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
+        <v>22</v>
+      </c>
+      <c r="H144" s="2">
+        <f>U86</f>
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C145" t="s">
+        <v>45</v>
+      </c>
+      <c r="D145" t="s">
+        <v>34</v>
+      </c>
+      <c r="E145">
+        <v>19</v>
+      </c>
+      <c r="F145" t="s">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
+        <v>21</v>
+      </c>
+      <c r="H145" s="2">
+        <f>X86</f>
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B896D3F-D36F-4760-A5D9-96A12E6A9B85}">
+  <dimension ref="A1:X73"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2"/>
+    <col min="18" max="18" width="12.21875" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" customWidth="1"/>
+    <col min="22" max="22" width="10.88671875" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2">
+        <f>R6</f>
+        <v>0.84</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2">
+        <f>S6</f>
+        <v>0.49</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="2">
+        <f>V6</f>
+        <v>0.88</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2">
+        <f>W6</f>
+        <v>0.24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2">
+        <f>T6</f>
+        <v>141.55427879702688</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="T6" s="6">
+        <v>141.55427879702688</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="W6" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="X6" s="5">
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2">
+        <f>Q6</f>
+        <v>1.33</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1.69</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="T7" s="6">
+        <v>183.68352843899919</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="W7" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="X7" s="5">
+        <v>2.4142857142857141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2">
+        <f>U6</f>
+        <v>0.89285714285714279</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1.82</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="T8" s="6">
+        <v>183.68352843899919</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1.6949152542372883</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="X8" s="5">
+        <v>3.0847457627118646</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2">
+        <f>X6</f>
+        <v>1.1875</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1.81</v>
+      </c>
+      <c r="R9" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="T9" s="6">
+        <v>171.88733853924694</v>
+      </c>
+      <c r="U9" s="5">
+        <v>1.9230769230769229</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="W9" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="X9" s="5">
+        <v>3.4807692307692304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <f>R7</f>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>1.9900000000000002</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="T10" s="6">
+        <v>183.68352843899919</v>
+      </c>
+      <c r="U10" s="5">
+        <v>1.9230769230769229</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="W10" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="X10" s="5">
+        <v>3.8269230769230771</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
+        <f>S7</f>
+        <v>0.6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="T11" s="6">
+        <v>171.88733853924694</v>
+      </c>
+      <c r="U11" s="5">
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="W11" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="X11" s="5">
+        <v>4.1458333333333339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="2">
+        <f>V7</f>
+        <v>0.47</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="4">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>2.6100000000000003</v>
+      </c>
+      <c r="R12" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="S12" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="T12" s="6">
+        <v>217.38692815257704</v>
+      </c>
+      <c r="U12" s="5">
+        <v>2.4390243902439024</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="X12" s="5">
+        <v>6.3658536585365857</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2">
+        <f>W7</f>
+        <v>0.23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2.7199999999999998</v>
+      </c>
+      <c r="R13" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="S13" s="5">
+        <v>1.42</v>
+      </c>
+      <c r="T13" s="6">
+        <v>219.07209813825588</v>
+      </c>
+      <c r="U13" s="5">
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="X13" s="5">
+        <v>6.4761904761904754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2">
+        <f>T7</f>
+        <v>183.68352843899919</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>2.77</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S14" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="T14" s="3">
+        <v>210.64624820986143</v>
+      </c>
+      <c r="U14" s="2">
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="X14" s="2">
+        <v>6.5952380952380949</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2">
+        <f>Q7</f>
+        <v>1.69</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2">
+        <f>U7</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="2">
+        <f>X7</f>
+        <v>2.4142857142857141</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2">
+        <f>R8</f>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2">
+        <f>S8</f>
+        <v>0.73</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="2">
+        <f>V8</f>
+        <v>0.36</v>
+      </c>
+      <c r="I20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="2">
+        <f>W8</f>
+        <v>0.23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2">
+        <f>T8</f>
+        <v>183.68352843899919</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2">
+        <f>Q8</f>
+        <v>1.82</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2">
+        <f>U8</f>
+        <v>1.6949152542372883</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="2">
+        <f>X8</f>
+        <v>3.0847457627118646</v>
+      </c>
+      <c r="I25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2">
+        <f>R9</f>
+        <v>1.02</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2">
+        <f>S9</f>
+        <v>0.79</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="2">
+        <f>V9</f>
+        <v>0.3</v>
+      </c>
+      <c r="I28" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="2">
+        <f>W9</f>
+        <v>0.22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="2">
+        <f>T9</f>
+        <v>171.88733853924694</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2">
+        <f>Q9</f>
+        <v>1.81</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="2">
+        <f>U9</f>
+        <v>1.9230769230769229</v>
+      </c>
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="2">
+        <f>X9</f>
+        <v>3.4807692307692304</v>
+      </c>
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2">
+        <f>R10</f>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="2">
+        <f>S10</f>
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="2">
+        <f>V10</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I36" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="2">
+        <f>W10</f>
+        <v>0.23</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2">
+        <f>T10</f>
+        <v>183.68352843899919</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2">
+        <f>Q10</f>
+        <v>1.9900000000000002</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="2">
+        <f>U10</f>
+        <v>1.9230769230769229</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="2">
+        <f>X10</f>
+        <v>3.8269230769230771</v>
+      </c>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2">
+        <f>R11</f>
+        <v>1.02</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="2">
+        <f>S11</f>
+        <v>0.97</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="2">
+        <f>V11</f>
+        <v>0.25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="2">
+        <f>W11</f>
+        <v>0.23</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2">
+        <f>T11</f>
+        <v>171.88733853924694</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2">
+        <f>Q11</f>
+        <v>1.99</v>
+      </c>
+      <c r="I47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="2">
+        <f>U11</f>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="2">
+        <f>X11</f>
+        <v>4.1458333333333339</v>
+      </c>
+      <c r="I49" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2">
+        <f>R12</f>
+        <v>1.29</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51">
+        <v>17</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2">
+        <f>S12</f>
+        <v>1.32</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52">
+        <v>17</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="2">
+        <f>V12</f>
+        <v>0.2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53">
+        <v>17</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" s="2">
+        <f>W12</f>
+        <v>0.21</v>
+      </c>
+      <c r="I53" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54">
+        <v>17</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="2">
+        <f>T12</f>
+        <v>217.38692815257704</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55">
+        <v>17</v>
+      </c>
+      <c r="F55" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2">
+        <f>Q12</f>
+        <v>2.6100000000000003</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56">
+        <v>17</v>
+      </c>
+      <c r="F56" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="2">
+        <f>U12</f>
+        <v>2.4390243902439024</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57">
+        <v>17</v>
+      </c>
+      <c r="F57" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" s="2">
+        <f>X12</f>
+        <v>6.3658536585365857</v>
+      </c>
+      <c r="I57" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58">
+        <v>18</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2">
+        <f>R13</f>
+        <v>1.3</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2">
+        <f>S13</f>
+        <v>1.42</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" s="2">
+        <f>V13</f>
+        <v>0.2</v>
+      </c>
+      <c r="I60" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>34</v>
+      </c>
+      <c r="E61">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" s="2">
+        <f>W13</f>
+        <v>0.22</v>
+      </c>
+      <c r="I61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="2">
+        <f>T13</f>
+        <v>219.07209813825588</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2">
+        <f>Q13</f>
+        <v>2.7199999999999998</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E64">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="2">
+        <f>U13</f>
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="I64" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="2">
+        <f>X13</f>
+        <v>6.4761904761904754</v>
+      </c>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66">
+        <v>19</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2">
+        <f>Q14</f>
+        <v>2.77</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2">
+        <f>R14</f>
+        <v>1.25</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" s="2">
+        <f>V14</f>
+        <v>0.19</v>
+      </c>
+      <c r="I68" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69">
+        <v>19</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+      <c r="H69" s="2">
+        <f>W14</f>
+        <v>0.23</v>
+      </c>
+      <c r="I69" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2">
+        <f>T14</f>
+        <v>210.64624820986143</v>
+      </c>
+      <c r="I70" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1</v>
+      </c>
+      <c r="B71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2">
+        <f>P14</f>
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>35</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="2">
+        <f>U14</f>
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" s="2">
+        <f>X14</f>
+        <v>6.5952380952380949</v>
+      </c>
+      <c r="I73" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eis2win-my.sharepoint.com/personal/caroline_adams_uksportsinstitute_co_uk/Documents/Documents/16_Msc_Biomech/Professional Practice/Assessment 2/Repo_Biomech_dashboard/Prof_Practice_Report/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{982CBBF7-6A9D-48B0-AF85-454491A8D7F1}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{835E9A0F-5C56-4BF8-837E-6CAA83E30B85}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="37">
   <si>
     <t>Cycle</t>
   </si>
@@ -150,33 +149,6 @@
     <t>60m_3</t>
   </si>
   <si>
-    <t>Rep3</t>
-  </si>
-  <si>
-    <t>Cycle Length (m)</t>
-  </si>
-  <si>
-    <t>Push Dist (m)</t>
-  </si>
-  <si>
-    <t>Recovery Dist (m)</t>
-  </si>
-  <si>
-    <t>Push Angle (deg)</t>
-  </si>
-  <si>
-    <t>Cycle Freq (Hz)</t>
-  </si>
-  <si>
-    <t>Push time (secs)</t>
-  </si>
-  <si>
-    <t>Recovery time (secs)</t>
-  </si>
-  <si>
-    <t>Avg Cycle Speed (m/s)</t>
-  </si>
-  <si>
     <t>third</t>
   </si>
 </sst>
@@ -184,7 +156,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,19 +170,19 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -225,16 +197,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +541,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
@@ -2928,7 +2896,7 @@
         <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s">
         <v>12</v>
@@ -2961,7 +2929,7 @@
         <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s">
         <v>12</v>
@@ -2994,7 +2962,7 @@
         <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s">
         <v>12</v>
@@ -3027,7 +2995,7 @@
         <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s">
         <v>12</v>
@@ -3060,7 +3028,7 @@
         <v>35</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s">
         <v>12</v>
@@ -3093,7 +3061,7 @@
         <v>35</v>
       </c>
       <c r="C79" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D79" t="s">
         <v>12</v>
@@ -3126,7 +3094,7 @@
         <v>35</v>
       </c>
       <c r="C80" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s">
         <v>12</v>
@@ -3159,7 +3127,7 @@
         <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s">
         <v>12</v>
@@ -3192,7 +3160,7 @@
         <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
@@ -3225,7 +3193,7 @@
         <v>35</v>
       </c>
       <c r="C83" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D83" t="s">
         <v>12</v>
@@ -3258,7 +3226,7 @@
         <v>35</v>
       </c>
       <c r="C84" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
@@ -3291,7 +3259,7 @@
         <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
@@ -3324,7 +3292,7 @@
         <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s">
         <v>12</v>
@@ -3357,7 +3325,7 @@
         <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
@@ -3390,7 +3358,7 @@
         <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -3423,7 +3391,7 @@
         <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
@@ -3456,7 +3424,7 @@
         <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
@@ -3489,7 +3457,7 @@
         <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
@@ -3522,7 +3490,7 @@
         <v>35</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s">
         <v>12</v>
@@ -3555,7 +3523,7 @@
         <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -3588,7 +3556,7 @@
         <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -3621,7 +3589,7 @@
         <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -3654,7 +3622,7 @@
         <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s">
         <v>12</v>
@@ -3687,7 +3655,7 @@
         <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s">
         <v>12</v>
@@ -3720,7 +3688,7 @@
         <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
@@ -3753,7 +3721,7 @@
         <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
         <v>12</v>
@@ -3786,7 +3754,7 @@
         <v>35</v>
       </c>
       <c r="C100" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s">
         <v>12</v>
@@ -3819,7 +3787,7 @@
         <v>35</v>
       </c>
       <c r="C101" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
         <v>12</v>
@@ -3852,7 +3820,7 @@
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s">
         <v>12</v>
@@ -3885,7 +3853,7 @@
         <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s">
         <v>12</v>
@@ -3918,7 +3886,7 @@
         <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s">
         <v>12</v>
@@ -3951,7 +3919,7 @@
         <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
         <v>12</v>
@@ -3984,7 +3952,7 @@
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s">
         <v>12</v>
@@ -4017,7 +3985,7 @@
         <v>35</v>
       </c>
       <c r="C107" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s">
         <v>12</v>
@@ -4050,7 +4018,7 @@
         <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s">
         <v>12</v>
@@ -4083,7 +4051,7 @@
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s">
         <v>12</v>
@@ -4116,7 +4084,7 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s">
         <v>12</v>
@@ -4149,7 +4117,7 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
         <v>12</v>
@@ -4182,7 +4150,7 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s">
         <v>12</v>
@@ -4215,7 +4183,7 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s">
         <v>12</v>
@@ -4248,7 +4216,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s">
         <v>12</v>
@@ -4281,7 +4249,7 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s">
         <v>12</v>
@@ -4314,7 +4282,7 @@
         <v>35</v>
       </c>
       <c r="C116" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s">
         <v>12</v>
@@ -4347,7 +4315,7 @@
         <v>35</v>
       </c>
       <c r="C117" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
         <v>12</v>
@@ -4380,7 +4348,7 @@
         <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s">
         <v>12</v>
@@ -4413,7 +4381,7 @@
         <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s">
         <v>12</v>
@@ -4446,7 +4414,7 @@
         <v>35</v>
       </c>
       <c r="C120" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D120" t="s">
         <v>12</v>
@@ -4479,7 +4447,7 @@
         <v>35</v>
       </c>
       <c r="C121" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s">
         <v>12</v>
@@ -4512,7 +4480,7 @@
         <v>35</v>
       </c>
       <c r="C122" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s">
         <v>34</v>
@@ -4545,7 +4513,7 @@
         <v>35</v>
       </c>
       <c r="C123" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s">
         <v>34</v>
@@ -4578,7 +4546,7 @@
         <v>35</v>
       </c>
       <c r="C124" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s">
         <v>34</v>
@@ -4611,7 +4579,7 @@
         <v>35</v>
       </c>
       <c r="C125" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s">
         <v>34</v>
@@ -4644,7 +4612,7 @@
         <v>35</v>
       </c>
       <c r="C126" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s">
         <v>34</v>
@@ -4677,7 +4645,7 @@
         <v>35</v>
       </c>
       <c r="C127" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s">
         <v>34</v>
@@ -4710,7 +4678,7 @@
         <v>35</v>
       </c>
       <c r="C128" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D128" t="s">
         <v>34</v>
@@ -4743,7 +4711,7 @@
         <v>35</v>
       </c>
       <c r="C129" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s">
         <v>34</v>
@@ -4776,7 +4744,7 @@
         <v>35</v>
       </c>
       <c r="C130" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s">
         <v>34</v>
@@ -4809,7 +4777,7 @@
         <v>35</v>
       </c>
       <c r="C131" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s">
         <v>34</v>
@@ -4842,7 +4810,7 @@
         <v>35</v>
       </c>
       <c r="C132" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s">
         <v>34</v>
@@ -4875,7 +4843,7 @@
         <v>35</v>
       </c>
       <c r="C133" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s">
         <v>34</v>
@@ -4908,7 +4876,7 @@
         <v>35</v>
       </c>
       <c r="C134" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D134" t="s">
         <v>34</v>
@@ -4941,7 +4909,7 @@
         <v>35</v>
       </c>
       <c r="C135" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s">
         <v>34</v>
@@ -4974,7 +4942,7 @@
         <v>35</v>
       </c>
       <c r="C136" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s">
         <v>34</v>
@@ -5007,7 +4975,7 @@
         <v>35</v>
       </c>
       <c r="C137" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s">
         <v>34</v>
@@ -5040,7 +5008,7 @@
         <v>35</v>
       </c>
       <c r="C138" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s">
         <v>34</v>
@@ -5073,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="C139" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s">
         <v>34</v>
@@ -5106,7 +5074,7 @@
         <v>35</v>
       </c>
       <c r="C140" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s">
         <v>34</v>
@@ -5139,7 +5107,7 @@
         <v>35</v>
       </c>
       <c r="C141" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s">
         <v>34</v>
@@ -5172,7 +5140,7 @@
         <v>35</v>
       </c>
       <c r="C142" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
         <v>34</v>
@@ -5205,7 +5173,7 @@
         <v>35</v>
       </c>
       <c r="C143" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s">
         <v>34</v>
@@ -5238,7 +5206,7 @@
         <v>35</v>
       </c>
       <c r="C144" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s">
         <v>34</v>
@@ -5271,7 +5239,7 @@
         <v>35</v>
       </c>
       <c r="C145" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s">
         <v>34</v>
@@ -5297,2730 +5265,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B896D3F-D36F-4760-A5D9-96A12E6A9B85}">
-  <dimension ref="A1:X73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="2"/>
-    <col min="18" max="18" width="12.21875" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" customWidth="1"/>
-    <col min="22" max="22" width="10.88671875" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2">
-        <f>R6</f>
-        <v>0.84</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2">
-        <f>S6</f>
-        <v>0.49</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="2">
-        <f>V6</f>
-        <v>0.88</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" t="s">
-        <v>36</v>
-      </c>
-      <c r="T4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="2">
-        <f>W6</f>
-        <v>0.24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" t="s">
-        <v>42</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2">
-        <f>T6</f>
-        <v>141.55427879702688</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>1.33</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="S6" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="T6" s="6">
-        <v>141.55427879702688</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0.89285714285714279</v>
-      </c>
-      <c r="V6" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="W6" s="5">
-        <v>0.24</v>
-      </c>
-      <c r="X6" s="5">
-        <v>1.1875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2">
-        <f>Q6</f>
-        <v>1.33</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1.69</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="S7" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="T7" s="6">
-        <v>183.68352843899919</v>
-      </c>
-      <c r="U7" s="5">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="V7" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="W7" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="X7" s="5">
-        <v>2.4142857142857141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="2">
-        <f>U6</f>
-        <v>0.89285714285714279</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>1.82</v>
-      </c>
-      <c r="R8" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="S8" s="5">
-        <v>0.73</v>
-      </c>
-      <c r="T8" s="6">
-        <v>183.68352843899919</v>
-      </c>
-      <c r="U8" s="5">
-        <v>1.6949152542372883</v>
-      </c>
-      <c r="V8" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="W8" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="X8" s="5">
-        <v>3.0847457627118646</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="2">
-        <f>X6</f>
-        <v>1.1875</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>1.81</v>
-      </c>
-      <c r="R9" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="S9" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="T9" s="6">
-        <v>171.88733853924694</v>
-      </c>
-      <c r="U9" s="5">
-        <v>1.9230769230769229</v>
-      </c>
-      <c r="V9" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="W9" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="X9" s="5">
-        <v>3.4807692307692304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2">
-        <f>R7</f>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>1.9900000000000002</v>
-      </c>
-      <c r="R10" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="S10" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="T10" s="6">
-        <v>183.68352843899919</v>
-      </c>
-      <c r="U10" s="5">
-        <v>1.9230769230769229</v>
-      </c>
-      <c r="V10" s="5">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="W10" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="X10" s="5">
-        <v>3.8269230769230771</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2">
-        <f>S7</f>
-        <v>0.6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="R11" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="S11" s="5">
-        <v>0.97</v>
-      </c>
-      <c r="T11" s="6">
-        <v>171.88733853924694</v>
-      </c>
-      <c r="U11" s="5">
-        <v>2.0833333333333335</v>
-      </c>
-      <c r="V11" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="W11" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="X11" s="5">
-        <v>4.1458333333333339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="2">
-        <f>V7</f>
-        <v>0.47</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" s="4">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="5">
-        <v>2.6100000000000003</v>
-      </c>
-      <c r="R12" s="5">
-        <v>1.29</v>
-      </c>
-      <c r="S12" s="5">
-        <v>1.32</v>
-      </c>
-      <c r="T12" s="6">
-        <v>217.38692815257704</v>
-      </c>
-      <c r="U12" s="5">
-        <v>2.4390243902439024</v>
-      </c>
-      <c r="V12" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="W12" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="X12" s="5">
-        <v>6.3658536585365857</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="2">
-        <f>W7</f>
-        <v>0.23</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="4">
-        <v>18</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>2.7199999999999998</v>
-      </c>
-      <c r="R13" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="S13" s="5">
-        <v>1.42</v>
-      </c>
-      <c r="T13" s="6">
-        <v>219.07209813825588</v>
-      </c>
-      <c r="U13" s="5">
-        <v>2.3809523809523809</v>
-      </c>
-      <c r="V13" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="W13" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="X13" s="5">
-        <v>6.4761904761904754</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2">
-        <f>T7</f>
-        <v>183.68352843899919</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>2.77</v>
-      </c>
-      <c r="R14" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="S14" s="2">
-        <v>1.52</v>
-      </c>
-      <c r="T14" s="3">
-        <v>210.64624820986143</v>
-      </c>
-      <c r="U14" s="2">
-        <v>2.3809523809523809</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="X14" s="2">
-        <v>6.5952380952380949</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2">
-        <f>Q7</f>
-        <v>1.69</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="2">
-        <f>U7</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="2">
-        <f>X7</f>
-        <v>2.4142857142857141</v>
-      </c>
-      <c r="I17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2">
-        <f>R8</f>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19">
-        <v>3</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2">
-        <f>S8</f>
-        <v>0.73</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="2">
-        <f>V8</f>
-        <v>0.36</v>
-      </c>
-      <c r="I20" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="2">
-        <f>W8</f>
-        <v>0.23</v>
-      </c>
-      <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="2">
-        <f>T8</f>
-        <v>183.68352843899919</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2">
-        <f>Q8</f>
-        <v>1.82</v>
-      </c>
-      <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="2">
-        <f>U8</f>
-        <v>1.6949152542372883</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="2">
-        <f>X8</f>
-        <v>3.0847457627118646</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2">
-        <f>R9</f>
-        <v>1.02</v>
-      </c>
-      <c r="I26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2">
-        <f>S9</f>
-        <v>0.79</v>
-      </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="2">
-        <f>V9</f>
-        <v>0.3</v>
-      </c>
-      <c r="I28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>1</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" s="2">
-        <f>W9</f>
-        <v>0.22</v>
-      </c>
-      <c r="I29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="2">
-        <f>T9</f>
-        <v>171.88733853924694</v>
-      </c>
-      <c r="I30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
-      <c r="F31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2">
-        <f>Q9</f>
-        <v>1.81</v>
-      </c>
-      <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
-      <c r="F32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="2">
-        <f>U9</f>
-        <v>1.9230769230769229</v>
-      </c>
-      <c r="I32" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33">
-        <v>4</v>
-      </c>
-      <c r="F33" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="2">
-        <f>X9</f>
-        <v>3.4807692307692304</v>
-      </c>
-      <c r="I33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="2">
-        <f>R10</f>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="2">
-        <f>S10</f>
-        <v>0.9</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>1</v>
-      </c>
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="2">
-        <f>V10</f>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I36" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="2">
-        <f>W10</f>
-        <v>0.23</v>
-      </c>
-      <c r="I37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="2">
-        <f>T10</f>
-        <v>183.68352843899919</v>
-      </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="2">
-        <f>Q10</f>
-        <v>1.9900000000000002</v>
-      </c>
-      <c r="I39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="2">
-        <f>U10</f>
-        <v>1.9230769230769229</v>
-      </c>
-      <c r="I40" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>1</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="2">
-        <f>X10</f>
-        <v>3.8269230769230771</v>
-      </c>
-      <c r="I41" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>1</v>
-      </c>
-      <c r="B42" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" t="s">
-        <v>30</v>
-      </c>
-      <c r="H42" s="2">
-        <f>R11</f>
-        <v>1.02</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>1</v>
-      </c>
-      <c r="B43" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" t="s">
-        <v>30</v>
-      </c>
-      <c r="H43" s="2">
-        <f>S11</f>
-        <v>0.97</v>
-      </c>
-      <c r="I43" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>1</v>
-      </c>
-      <c r="B44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" s="2">
-        <f>V11</f>
-        <v>0.25</v>
-      </c>
-      <c r="I44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>1</v>
-      </c>
-      <c r="B45" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" s="2">
-        <f>W11</f>
-        <v>0.23</v>
-      </c>
-      <c r="I45" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>1</v>
-      </c>
-      <c r="B46" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="2">
-        <f>T11</f>
-        <v>171.88733853924694</v>
-      </c>
-      <c r="I46" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>1</v>
-      </c>
-      <c r="B47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H47" s="2">
-        <f>Q11</f>
-        <v>1.99</v>
-      </c>
-      <c r="I47" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>1</v>
-      </c>
-      <c r="B48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="2">
-        <f>U11</f>
-        <v>2.0833333333333335</v>
-      </c>
-      <c r="I48" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>1</v>
-      </c>
-      <c r="B49" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="2">
-        <f>X11</f>
-        <v>4.1458333333333339</v>
-      </c>
-      <c r="I49" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>1</v>
-      </c>
-      <c r="B50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50">
-        <v>17</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" t="s">
-        <v>30</v>
-      </c>
-      <c r="H50" s="2">
-        <f>R12</f>
-        <v>1.29</v>
-      </c>
-      <c r="I50" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>1</v>
-      </c>
-      <c r="B51" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51">
-        <v>17</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" t="s">
-        <v>30</v>
-      </c>
-      <c r="H51" s="2">
-        <f>S12</f>
-        <v>1.32</v>
-      </c>
-      <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>1</v>
-      </c>
-      <c r="B52" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" t="s">
-        <v>34</v>
-      </c>
-      <c r="E52">
-        <v>17</v>
-      </c>
-      <c r="F52" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" t="s">
-        <v>31</v>
-      </c>
-      <c r="H52" s="2">
-        <f>V12</f>
-        <v>0.2</v>
-      </c>
-      <c r="I52" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>1</v>
-      </c>
-      <c r="B53" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" t="s">
-        <v>34</v>
-      </c>
-      <c r="E53">
-        <v>17</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" t="s">
-        <v>31</v>
-      </c>
-      <c r="H53" s="2">
-        <f>W12</f>
-        <v>0.21</v>
-      </c>
-      <c r="I53" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>1</v>
-      </c>
-      <c r="B54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54">
-        <v>17</v>
-      </c>
-      <c r="F54" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="2">
-        <f>T12</f>
-        <v>217.38692815257704</v>
-      </c>
-      <c r="I54" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>1</v>
-      </c>
-      <c r="B55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" t="s">
-        <v>34</v>
-      </c>
-      <c r="E55">
-        <v>17</v>
-      </c>
-      <c r="F55" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>30</v>
-      </c>
-      <c r="H55" s="2">
-        <f>Q12</f>
-        <v>2.6100000000000003</v>
-      </c>
-      <c r="I55" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>1</v>
-      </c>
-      <c r="B56" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" t="s">
-        <v>34</v>
-      </c>
-      <c r="E56">
-        <v>17</v>
-      </c>
-      <c r="F56" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="2">
-        <f>U12</f>
-        <v>2.4390243902439024</v>
-      </c>
-      <c r="I56" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>1</v>
-      </c>
-      <c r="B57" t="s">
-        <v>35</v>
-      </c>
-      <c r="C57" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" t="s">
-        <v>34</v>
-      </c>
-      <c r="E57">
-        <v>17</v>
-      </c>
-      <c r="F57" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>21</v>
-      </c>
-      <c r="H57" s="2">
-        <f>X12</f>
-        <v>6.3658536585365857</v>
-      </c>
-      <c r="I57" t="s">
-        <v>19</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>1</v>
-      </c>
-      <c r="B58" t="s">
-        <v>35</v>
-      </c>
-      <c r="C58" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58">
-        <v>18</v>
-      </c>
-      <c r="F58" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="2">
-        <f>R13</f>
-        <v>1.3</v>
-      </c>
-      <c r="I58" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>1</v>
-      </c>
-      <c r="B59" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59">
-        <v>18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>30</v>
-      </c>
-      <c r="H59" s="2">
-        <f>S13</f>
-        <v>1.42</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>1</v>
-      </c>
-      <c r="B60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60">
-        <v>18</v>
-      </c>
-      <c r="F60" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" t="s">
-        <v>31</v>
-      </c>
-      <c r="H60" s="2">
-        <f>V13</f>
-        <v>0.2</v>
-      </c>
-      <c r="I60" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>1</v>
-      </c>
-      <c r="B61" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" t="s">
-        <v>34</v>
-      </c>
-      <c r="E61">
-        <v>18</v>
-      </c>
-      <c r="F61" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" s="2">
-        <f>W13</f>
-        <v>0.22</v>
-      </c>
-      <c r="I61" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>1</v>
-      </c>
-      <c r="B62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" t="s">
-        <v>34</v>
-      </c>
-      <c r="E62">
-        <v>18</v>
-      </c>
-      <c r="F62" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" s="2">
-        <f>T13</f>
-        <v>219.07209813825588</v>
-      </c>
-      <c r="I62" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>1</v>
-      </c>
-      <c r="B63" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" t="s">
-        <v>34</v>
-      </c>
-      <c r="E63">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
-        <v>30</v>
-      </c>
-      <c r="H63" s="2">
-        <f>Q13</f>
-        <v>2.7199999999999998</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>1</v>
-      </c>
-      <c r="B64" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" t="s">
-        <v>34</v>
-      </c>
-      <c r="E64">
-        <v>18</v>
-      </c>
-      <c r="F64" t="s">
-        <v>0</v>
-      </c>
-      <c r="G64" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="2">
-        <f>U13</f>
-        <v>2.3809523809523809</v>
-      </c>
-      <c r="I64" t="s">
-        <v>18</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>1</v>
-      </c>
-      <c r="B65" t="s">
-        <v>35</v>
-      </c>
-      <c r="C65" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" t="s">
-        <v>34</v>
-      </c>
-      <c r="E65">
-        <v>18</v>
-      </c>
-      <c r="F65" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65" s="2">
-        <f>X13</f>
-        <v>6.4761904761904754</v>
-      </c>
-      <c r="I65" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>1</v>
-      </c>
-      <c r="B66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C66" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" t="s">
-        <v>34</v>
-      </c>
-      <c r="E66">
-        <v>19</v>
-      </c>
-      <c r="F66" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" t="s">
-        <v>30</v>
-      </c>
-      <c r="H66" s="2">
-        <f>Q14</f>
-        <v>2.77</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>1</v>
-      </c>
-      <c r="B67" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" t="s">
-        <v>34</v>
-      </c>
-      <c r="E67">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" t="s">
-        <v>30</v>
-      </c>
-      <c r="H67" s="2">
-        <f>R14</f>
-        <v>1.25</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>1</v>
-      </c>
-      <c r="B68" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" t="s">
-        <v>34</v>
-      </c>
-      <c r="E68">
-        <v>19</v>
-      </c>
-      <c r="F68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" t="s">
-        <v>31</v>
-      </c>
-      <c r="H68" s="2">
-        <f>V14</f>
-        <v>0.19</v>
-      </c>
-      <c r="I68" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>1</v>
-      </c>
-      <c r="B69" t="s">
-        <v>35</v>
-      </c>
-      <c r="C69" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E69">
-        <v>19</v>
-      </c>
-      <c r="F69" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" t="s">
-        <v>31</v>
-      </c>
-      <c r="H69" s="2">
-        <f>W14</f>
-        <v>0.23</v>
-      </c>
-      <c r="I69" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>1</v>
-      </c>
-      <c r="B70" t="s">
-        <v>35</v>
-      </c>
-      <c r="C70" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" t="s">
-        <v>34</v>
-      </c>
-      <c r="E70">
-        <v>19</v>
-      </c>
-      <c r="F70" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="2">
-        <f>T14</f>
-        <v>210.64624820986143</v>
-      </c>
-      <c r="I70" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>35</v>
-      </c>
-      <c r="C71" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" t="s">
-        <v>34</v>
-      </c>
-      <c r="E71">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>30</v>
-      </c>
-      <c r="H71" s="2">
-        <f>P14</f>
-        <v>19</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>1</v>
-      </c>
-      <c r="B72" t="s">
-        <v>35</v>
-      </c>
-      <c r="C72" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E72">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" s="2">
-        <f>U14</f>
-        <v>2.3809523809523809</v>
-      </c>
-      <c r="I72" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>1</v>
-      </c>
-      <c r="B73" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" t="s">
-        <v>34</v>
-      </c>
-      <c r="E73">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="2">
-        <f>X14</f>
-        <v>6.5952380952380949</v>
-      </c>
-      <c r="I73" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eis2win-my.sharepoint.com/personal/caroline_adams_uksportsinstitute_co_uk/Documents/Documents/16_Msc_Biomech/Professional Practice/Assessment 2/Repo_Biomech_dashboard/Prof_Practice_Report/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{835E9A0F-5C56-4BF8-837E-6CAA83E30B85}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07008F1B-B000-4DB2-BE8D-61D9F623F67A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
@@ -156,7 +156,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,12 +169,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -541,7 +535,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
@@ -2911,8 +2905,7 @@
         <v>30</v>
       </c>
       <c r="H74" s="2">
-        <f>R78</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
@@ -2944,8 +2937,7 @@
         <v>30</v>
       </c>
       <c r="H75" s="2">
-        <f>S78</f>
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
@@ -2977,8 +2969,7 @@
         <v>31</v>
       </c>
       <c r="H76" s="2">
-        <f>V78</f>
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="I76" t="s">
         <v>16</v>
@@ -3010,8 +3001,7 @@
         <v>31</v>
       </c>
       <c r="H77" s="2">
-        <f>W78</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I77" t="s">
         <v>16</v>
@@ -3043,8 +3033,7 @@
         <v>20</v>
       </c>
       <c r="H78" s="2">
-        <f>T78</f>
-        <v>0</v>
+        <v>141.55427879702688</v>
       </c>
       <c r="I78" t="s">
         <v>17</v>
@@ -3076,8 +3065,7 @@
         <v>30</v>
       </c>
       <c r="H79" s="2">
-        <f>Q78</f>
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
@@ -3109,8 +3097,7 @@
         <v>22</v>
       </c>
       <c r="H80" s="2">
-        <f>U78</f>
-        <v>0</v>
+        <v>0.89285714285714279</v>
       </c>
       <c r="I80" t="s">
         <v>18</v>
@@ -3142,8 +3129,7 @@
         <v>21</v>
       </c>
       <c r="H81" s="2">
-        <f>X78</f>
-        <v>0</v>
+        <v>1.1875</v>
       </c>
       <c r="I81" t="s">
         <v>19</v>
@@ -3175,8 +3161,7 @@
         <v>30</v>
       </c>
       <c r="H82" s="2">
-        <f>R79</f>
-        <v>0</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
@@ -3208,8 +3193,7 @@
         <v>30</v>
       </c>
       <c r="H83" s="2">
-        <f>S79</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
@@ -3241,8 +3225,7 @@
         <v>31</v>
       </c>
       <c r="H84" s="2">
-        <f>V79</f>
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="I84" t="s">
         <v>16</v>
@@ -3274,8 +3257,7 @@
         <v>31</v>
       </c>
       <c r="H85" s="2">
-        <f>W79</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I85" t="s">
         <v>16</v>
@@ -3307,8 +3289,7 @@
         <v>20</v>
       </c>
       <c r="H86" s="2">
-        <f>T79</f>
-        <v>0</v>
+        <v>183.68352843899919</v>
       </c>
       <c r="I86" t="s">
         <v>17</v>
@@ -3340,8 +3321,7 @@
         <v>30</v>
       </c>
       <c r="H87" s="2">
-        <f>Q79</f>
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
@@ -3373,8 +3353,7 @@
         <v>22</v>
       </c>
       <c r="H88" s="2">
-        <f>U79</f>
-        <v>0</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="I88" t="s">
         <v>18</v>
@@ -3406,8 +3385,7 @@
         <v>21</v>
       </c>
       <c r="H89" s="2">
-        <f>X79</f>
-        <v>0</v>
+        <v>2.4142857142857141</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
@@ -3439,8 +3417,7 @@
         <v>30</v>
       </c>
       <c r="H90" s="2">
-        <f>R80</f>
-        <v>0</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
@@ -3472,8 +3449,7 @@
         <v>30</v>
       </c>
       <c r="H91" s="2">
-        <f>S80</f>
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
@@ -3505,8 +3481,7 @@
         <v>31</v>
       </c>
       <c r="H92" s="2">
-        <f>V80</f>
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="I92" t="s">
         <v>16</v>
@@ -3538,8 +3513,7 @@
         <v>31</v>
       </c>
       <c r="H93" s="2">
-        <f>W80</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I93" t="s">
         <v>16</v>
@@ -3571,8 +3545,7 @@
         <v>20</v>
       </c>
       <c r="H94" s="2">
-        <f>T80</f>
-        <v>0</v>
+        <v>183.68352843899919</v>
       </c>
       <c r="I94" t="s">
         <v>17</v>
@@ -3604,8 +3577,7 @@
         <v>30</v>
       </c>
       <c r="H95" s="2">
-        <f>Q80</f>
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
@@ -3637,8 +3609,7 @@
         <v>22</v>
       </c>
       <c r="H96" s="2">
-        <f>U80</f>
-        <v>0</v>
+        <v>1.6949152542372883</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
@@ -3670,8 +3641,7 @@
         <v>21</v>
       </c>
       <c r="H97" s="2">
-        <f>X80</f>
-        <v>0</v>
+        <v>3.0847457627118646</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
@@ -3703,8 +3673,7 @@
         <v>30</v>
       </c>
       <c r="H98" s="2">
-        <f>R81</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
@@ -3736,8 +3705,7 @@
         <v>30</v>
       </c>
       <c r="H99" s="2">
-        <f>S81</f>
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
@@ -3769,8 +3737,7 @@
         <v>31</v>
       </c>
       <c r="H100" s="2">
-        <f>V81</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I100" t="s">
         <v>16</v>
@@ -3802,8 +3769,7 @@
         <v>31</v>
       </c>
       <c r="H101" s="2">
-        <f>W81</f>
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I101" t="s">
         <v>16</v>
@@ -3835,8 +3801,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="2">
-        <f>T81</f>
-        <v>0</v>
+        <v>171.88733853924694</v>
       </c>
       <c r="I102" t="s">
         <v>17</v>
@@ -3868,8 +3833,7 @@
         <v>30</v>
       </c>
       <c r="H103" s="2">
-        <f>Q81</f>
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
@@ -3901,8 +3865,7 @@
         <v>22</v>
       </c>
       <c r="H104" s="2">
-        <f>U81</f>
-        <v>0</v>
+        <v>1.9230769230769229</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -3934,8 +3897,7 @@
         <v>21</v>
       </c>
       <c r="H105" s="2">
-        <f>X81</f>
-        <v>0</v>
+        <v>3.4807692307692304</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
@@ -3967,8 +3929,7 @@
         <v>30</v>
       </c>
       <c r="H106" s="2">
-        <f>R82</f>
-        <v>0</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
@@ -4000,8 +3961,7 @@
         <v>30</v>
       </c>
       <c r="H107" s="2">
-        <f>S82</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
@@ -4033,8 +3993,7 @@
         <v>31</v>
       </c>
       <c r="H108" s="2">
-        <f>V82</f>
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I108" t="s">
         <v>16</v>
@@ -4066,8 +4025,7 @@
         <v>31</v>
       </c>
       <c r="H109" s="2">
-        <f>W82</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I109" t="s">
         <v>16</v>
@@ -4099,8 +4057,7 @@
         <v>20</v>
       </c>
       <c r="H110" s="2">
-        <f>T82</f>
-        <v>0</v>
+        <v>183.68352843899919</v>
       </c>
       <c r="I110" t="s">
         <v>17</v>
@@ -4132,8 +4089,7 @@
         <v>30</v>
       </c>
       <c r="H111" s="2">
-        <f>Q82</f>
-        <v>0</v>
+        <v>1.9900000000000002</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
@@ -4165,8 +4121,7 @@
         <v>22</v>
       </c>
       <c r="H112" s="2">
-        <f>U82</f>
-        <v>0</v>
+        <v>1.9230769230769229</v>
       </c>
       <c r="I112" t="s">
         <v>18</v>
@@ -4198,8 +4153,7 @@
         <v>21</v>
       </c>
       <c r="H113" s="2">
-        <f>X82</f>
-        <v>0</v>
+        <v>3.8269230769230771</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
@@ -4231,8 +4185,7 @@
         <v>30</v>
       </c>
       <c r="H114" s="2">
-        <f>R83</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
@@ -4264,8 +4217,7 @@
         <v>30</v>
       </c>
       <c r="H115" s="2">
-        <f>S83</f>
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="I115" t="s">
         <v>15</v>
@@ -4297,8 +4249,7 @@
         <v>31</v>
       </c>
       <c r="H116" s="2">
-        <f>V83</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I116" t="s">
         <v>16</v>
@@ -4330,8 +4281,7 @@
         <v>31</v>
       </c>
       <c r="H117" s="2">
-        <f>W83</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I117" t="s">
         <v>16</v>
@@ -4363,8 +4313,7 @@
         <v>20</v>
       </c>
       <c r="H118" s="2">
-        <f>T83</f>
-        <v>0</v>
+        <v>171.88733853924694</v>
       </c>
       <c r="I118" t="s">
         <v>17</v>
@@ -4396,8 +4345,7 @@
         <v>30</v>
       </c>
       <c r="H119" s="2">
-        <f>Q83</f>
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
@@ -4429,8 +4377,7 @@
         <v>22</v>
       </c>
       <c r="H120" s="2">
-        <f>U83</f>
-        <v>0</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="I120" t="s">
         <v>18</v>
@@ -4462,8 +4409,7 @@
         <v>21</v>
       </c>
       <c r="H121" s="2">
-        <f>X83</f>
-        <v>0</v>
+        <v>4.1458333333333339</v>
       </c>
       <c r="I121" t="s">
         <v>19</v>
@@ -4495,8 +4441,7 @@
         <v>30</v>
       </c>
       <c r="H122" s="2">
-        <f>R84</f>
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I122" t="s">
         <v>15</v>
@@ -4528,8 +4473,7 @@
         <v>30</v>
       </c>
       <c r="H123" s="2">
-        <f>S84</f>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="I123" t="s">
         <v>15</v>
@@ -4561,8 +4505,7 @@
         <v>31</v>
       </c>
       <c r="H124" s="2">
-        <f>V84</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I124" t="s">
         <v>16</v>
@@ -4594,8 +4537,7 @@
         <v>31</v>
       </c>
       <c r="H125" s="2">
-        <f>W84</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="I125" t="s">
         <v>16</v>
@@ -4627,8 +4569,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="2">
-        <f>T84</f>
-        <v>0</v>
+        <v>217.38692815257704</v>
       </c>
       <c r="I126" t="s">
         <v>17</v>
@@ -4660,8 +4601,7 @@
         <v>30</v>
       </c>
       <c r="H127" s="2">
-        <f>Q84</f>
-        <v>0</v>
+        <v>2.6100000000000003</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
@@ -4693,8 +4633,7 @@
         <v>22</v>
       </c>
       <c r="H128" s="2">
-        <f>U84</f>
-        <v>0</v>
+        <v>2.4390243902439024</v>
       </c>
       <c r="I128" t="s">
         <v>18</v>
@@ -4726,8 +4665,7 @@
         <v>21</v>
       </c>
       <c r="H129" s="2">
-        <f>X84</f>
-        <v>0</v>
+        <v>6.3658536585365857</v>
       </c>
       <c r="I129" t="s">
         <v>19</v>
@@ -4759,8 +4697,7 @@
         <v>30</v>
       </c>
       <c r="H130" s="2">
-        <f>R85</f>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I130" t="s">
         <v>15</v>
@@ -4792,8 +4729,7 @@
         <v>30</v>
       </c>
       <c r="H131" s="2">
-        <f>S85</f>
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="I131" t="s">
         <v>15</v>
@@ -4825,8 +4761,7 @@
         <v>31</v>
       </c>
       <c r="H132" s="2">
-        <f>V85</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I132" t="s">
         <v>16</v>
@@ -4858,8 +4793,7 @@
         <v>31</v>
       </c>
       <c r="H133" s="2">
-        <f>W85</f>
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I133" t="s">
         <v>16</v>
@@ -4891,8 +4825,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="2">
-        <f>T85</f>
-        <v>0</v>
+        <v>219.07209813825588</v>
       </c>
       <c r="I134" t="s">
         <v>17</v>
@@ -4924,8 +4857,7 @@
         <v>30</v>
       </c>
       <c r="H135" s="2">
-        <f>Q85</f>
-        <v>0</v>
+        <v>2.7199999999999998</v>
       </c>
       <c r="I135" t="s">
         <v>15</v>
@@ -4957,8 +4889,7 @@
         <v>22</v>
       </c>
       <c r="H136" s="2">
-        <f>U85</f>
-        <v>0</v>
+        <v>2.3809523809523809</v>
       </c>
       <c r="I136" t="s">
         <v>18</v>
@@ -4990,8 +4921,7 @@
         <v>21</v>
       </c>
       <c r="H137" s="2">
-        <f>X85</f>
-        <v>0</v>
+        <v>6.4761904761904754</v>
       </c>
       <c r="I137" t="s">
         <v>19</v>
@@ -5023,8 +4953,7 @@
         <v>30</v>
       </c>
       <c r="H138" s="2">
-        <f>Q86</f>
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
@@ -5056,8 +4985,7 @@
         <v>30</v>
       </c>
       <c r="H139" s="2">
-        <f>R86</f>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="I139" t="s">
         <v>15</v>
@@ -5089,8 +5017,7 @@
         <v>31</v>
       </c>
       <c r="H140" s="2">
-        <f>V86</f>
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="I140" t="s">
         <v>16</v>
@@ -5122,8 +5049,7 @@
         <v>31</v>
       </c>
       <c r="H141" s="2">
-        <f>W86</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I141" t="s">
         <v>16</v>
@@ -5155,8 +5081,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="2">
-        <f>T86</f>
-        <v>0</v>
+        <v>210.64624820986143</v>
       </c>
       <c r="I142" t="s">
         <v>17</v>
@@ -5188,8 +5113,7 @@
         <v>30</v>
       </c>
       <c r="H143" s="2">
-        <f>P86</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I143" t="s">
         <v>15</v>
@@ -5221,8 +5145,7 @@
         <v>22</v>
       </c>
       <c r="H144" s="2">
-        <f>U86</f>
-        <v>0</v>
+        <v>2.3809523809523809</v>
       </c>
       <c r="I144" t="s">
         <v>18</v>
@@ -5254,8 +5177,7 @@
         <v>21</v>
       </c>
       <c r="H145" s="2">
-        <f>X86</f>
-        <v>0</v>
+        <v>6.5952380952380949</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -5265,7 +5187,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eis2win-my.sharepoint.com/personal/caroline_adams_uksportsinstitute_co_uk/Documents/Documents/16_Msc_Biomech/Professional Practice/Assessment 2/Repo_Biomech_dashboard/Prof_Practice_Report/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07008F1B-B000-4DB2-BE8D-61D9F623F67A}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D497B0-BF6D-48F5-8E1B-44B33C70FBBA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
@@ -4953,7 +4953,7 @@
         <v>30</v>
       </c>
       <c r="H138" s="2">
-        <v>2.77</v>
+        <v>1.25</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="H139" s="2">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="I139" t="s">
         <v>15</v>
@@ -5113,7 +5113,7 @@
         <v>30</v>
       </c>
       <c r="H143" s="2">
-        <v>19</v>
+        <v>2.77</v>
       </c>
       <c r="I143" t="s">
         <v>15</v>

--- a/data/60m_push_breakdown.xlsx
+++ b/data/60m_push_breakdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eis2win-my.sharepoint.com/personal/caroline_adams_uksportsinstitute_co_uk/Documents/Documents/16_Msc_Biomech/Professional Practice/Assessment 2/Repo_Biomech_dashboard/Prof_Practice_Report/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D497B0-BF6D-48F5-8E1B-44B33C70FBBA}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{A53084EA-BA0C-4D14-A61B-B1C365EC53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93EC0740-577C-4334-B797-B4C932985632}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0658653D-6FC8-4E80-8C2B-51B3DC0ABD69}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9ED8C8E-FDDF-49A2-ABF2-02E1268CE5AD}">
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -546,7 +546,7 @@
     <col min="10" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -578,7 +578,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -609,8 +609,9 @@
       <c r="J2" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -642,7 +643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -674,7 +675,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -706,7 +707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -738,7 +739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -770,7 +771,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -802,7 +803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -834,7 +835,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -865,8 +866,9 @@
       <c r="J10" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -898,7 +900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -930,7 +932,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -962,7 +964,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -994,7 +996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1026,7 +1028,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
